--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/1.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/1.xlsx
@@ -426,13 +426,13 @@
         <v>-17.10683048150493</v>
       </c>
       <c r="E2">
-        <v>-5.899720656270582</v>
+        <v>-4.308659427571633</v>
       </c>
       <c r="F2">
-        <v>-4.390238865955121</v>
+        <v>-4.301646628960519</v>
       </c>
       <c r="G2">
-        <v>-5.377042184281224</v>
+        <v>-5.646437827539417</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.06094195560098</v>
       </c>
       <c r="E3">
-        <v>-4.574843129742496</v>
+        <v>-4.511779600711678</v>
       </c>
       <c r="F3">
-        <v>-4.838012865538394</v>
+        <v>-4.146495071150977</v>
       </c>
       <c r="G3">
-        <v>-6.241604394044052</v>
+        <v>-5.553563782980703</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.26688607397592</v>
       </c>
       <c r="E4">
-        <v>-5.119763464033485</v>
+        <v>-5.298556674804327</v>
       </c>
       <c r="F4">
-        <v>-4.629521073927786</v>
+        <v>-4.273511958491837</v>
       </c>
       <c r="G4">
-        <v>-4.861017519438406</v>
+        <v>-5.363455705388056</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-20.55077241229307</v>
       </c>
       <c r="E5">
-        <v>-5.708397157920517</v>
+        <v>-6.024276333851555</v>
       </c>
       <c r="F5">
-        <v>-4.381506216794809</v>
+        <v>-4.228410666879015</v>
       </c>
       <c r="G5">
-        <v>-5.378627935594535</v>
+        <v>-5.393376415971988</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-21.85879256925985</v>
       </c>
       <c r="E6">
-        <v>-6.575935037465958</v>
+        <v>-7.541958169730214</v>
       </c>
       <c r="F6">
-        <v>-4.791766770174902</v>
+        <v>-3.674864090367079</v>
       </c>
       <c r="G6">
-        <v>-5.227869002281665</v>
+        <v>-5.735163758537424</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-23.08111786592139</v>
       </c>
       <c r="E7">
-        <v>-7.388257233435874</v>
+        <v>-7.792563921314692</v>
       </c>
       <c r="F7">
-        <v>-4.578791854180344</v>
+        <v>-4.201545055271422</v>
       </c>
       <c r="G7">
-        <v>-5.569934430672399</v>
+        <v>-5.503362670423195</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-24.13885764622363</v>
       </c>
       <c r="E8">
-        <v>-9.79317581079334</v>
+        <v>-8.226926091182417</v>
       </c>
       <c r="F8">
-        <v>-4.438663567587974</v>
+        <v>-4.181464601060158</v>
       </c>
       <c r="G8">
-        <v>-5.650705120739538</v>
+        <v>-5.724338274624007</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-24.93537059108565</v>
       </c>
       <c r="E9">
-        <v>-9.362472647923813</v>
+        <v>-8.797631556473082</v>
       </c>
       <c r="F9">
-        <v>-4.297563606032121</v>
+        <v>-3.726190563011939</v>
       </c>
       <c r="G9">
-        <v>-5.460894992245424</v>
+        <v>-4.857263360796873</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-25.40086958054496</v>
       </c>
       <c r="E10">
-        <v>-9.750943262197806</v>
+        <v>-8.989715838456435</v>
       </c>
       <c r="F10">
-        <v>-4.281071639409785</v>
+        <v>-3.957018453271632</v>
       </c>
       <c r="G10">
-        <v>-4.985500652806082</v>
+        <v>-5.118336292569338</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-25.47771174654645</v>
       </c>
       <c r="E11">
-        <v>-10.72582408962107</v>
+        <v>-10.74110768939695</v>
       </c>
       <c r="F11">
-        <v>-4.365884864312815</v>
+        <v>-3.538239797888551</v>
       </c>
       <c r="G11">
-        <v>-4.253284122066698</v>
+        <v>-5.38028982945525</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-25.14520410241677</v>
       </c>
       <c r="E12">
-        <v>-11.16676160374793</v>
+        <v>-11.00484148712967</v>
       </c>
       <c r="F12">
-        <v>-4.054032701650496</v>
+        <v>-3.447927041798335</v>
       </c>
       <c r="G12">
-        <v>-4.003341244397263</v>
+        <v>-4.669164784346563</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-24.39349864703764</v>
       </c>
       <c r="E13">
-        <v>-11.17835902568157</v>
+        <v>-11.82223104551417</v>
       </c>
       <c r="F13">
-        <v>-3.791635729670114</v>
+        <v>-3.383572835009647</v>
       </c>
       <c r="G13">
-        <v>-4.287720416766197</v>
+        <v>-4.283585545387647</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-23.25180444731302</v>
       </c>
       <c r="E14">
-        <v>-12.11508745959021</v>
+        <v>-12.51663630679836</v>
       </c>
       <c r="F14">
-        <v>-3.58627268173988</v>
+        <v>-3.127494649577819</v>
       </c>
       <c r="G14">
-        <v>-3.569173128558464</v>
+        <v>-3.790307638945162</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-21.77123231427815</v>
       </c>
       <c r="E15">
-        <v>-13.17867203587572</v>
+        <v>-13.18343599053178</v>
       </c>
       <c r="F15">
-        <v>-3.490812450608668</v>
+        <v>-3.157401197921089</v>
       </c>
       <c r="G15">
-        <v>-3.996097770757338</v>
+        <v>-3.190969785061046</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-20.02037215648668</v>
       </c>
       <c r="E16">
-        <v>-13.39853850589613</v>
+        <v>-14.17547520597011</v>
       </c>
       <c r="F16">
-        <v>-3.14302073980849</v>
+        <v>-2.890060529280799</v>
       </c>
       <c r="G16">
-        <v>-3.559509646129332</v>
+        <v>-2.899479560873757</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-18.07908731617364</v>
       </c>
       <c r="E17">
-        <v>-14.84455271212939</v>
+        <v>-14.76077141451348</v>
       </c>
       <c r="F17">
-        <v>-3.100666314503351</v>
+        <v>-2.689956785990939</v>
       </c>
       <c r="G17">
-        <v>-2.293371641361831</v>
+        <v>-2.233219028913274</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-16.04414640122425</v>
       </c>
       <c r="E18">
-        <v>-14.97200208460127</v>
+        <v>-16.36240663002035</v>
       </c>
       <c r="F18">
-        <v>-2.591344616892075</v>
+        <v>-1.996585105356058</v>
       </c>
       <c r="G18">
-        <v>-2.186454262625529</v>
+        <v>-1.927460353451726</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-14.01699460607192</v>
       </c>
       <c r="E19">
-        <v>-16.89584728270189</v>
+        <v>-16.49627285016109</v>
       </c>
       <c r="F19">
-        <v>-2.351683016648928</v>
+        <v>-1.767327799692073</v>
       </c>
       <c r="G19">
-        <v>-1.236172097214352</v>
+        <v>-2.008191316972393</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.08623835173519</v>
       </c>
       <c r="E20">
-        <v>-17.54000912487097</v>
+        <v>-17.35833127615725</v>
       </c>
       <c r="F20">
-        <v>-2.257765205621728</v>
+        <v>-1.563244579399164</v>
       </c>
       <c r="G20">
-        <v>-1.198190208242294</v>
+        <v>-1.837595594788209</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.34481939465659</v>
       </c>
       <c r="E21">
-        <v>-18.7352047412414</v>
+        <v>-18.64246612203832</v>
       </c>
       <c r="F21">
-        <v>-1.970881693214592</v>
+        <v>-1.464736784593052</v>
       </c>
       <c r="G21">
-        <v>-2.071535295320808</v>
+        <v>-1.211548259493253</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.871599406041183</v>
       </c>
       <c r="E22">
-        <v>-19.17542675647505</v>
+        <v>-18.56855689775914</v>
       </c>
       <c r="F22">
-        <v>-1.634429503791337</v>
+        <v>-1.195207569274566</v>
       </c>
       <c r="G22">
-        <v>-1.299506143926149</v>
+        <v>-1.331671404385708</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.731079173595102</v>
       </c>
       <c r="E23">
-        <v>-19.32707176556991</v>
+        <v>-19.02971404833024</v>
       </c>
       <c r="F23">
-        <v>-1.440285035597217</v>
+        <v>-0.9016407886616437</v>
       </c>
       <c r="G23">
-        <v>-0.9243120863239279</v>
+        <v>-1.498473241381887</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.957324596192327</v>
       </c>
       <c r="E24">
-        <v>-19.74530351102232</v>
+        <v>-20.34181222120869</v>
       </c>
       <c r="F24">
-        <v>-1.192075512124581</v>
+        <v>-0.4455789732133618</v>
       </c>
       <c r="G24">
-        <v>-1.285856764667734</v>
+        <v>-1.230011171965768</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.571632452576093</v>
       </c>
       <c r="E25">
-        <v>-20.51094166844716</v>
+        <v>-20.19735842883801</v>
       </c>
       <c r="F25">
-        <v>-0.9454730214133766</v>
+        <v>-0.4784726144111274</v>
       </c>
       <c r="G25">
-        <v>-1.411819711891464</v>
+        <v>-1.757884279293638</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.567324634134525</v>
       </c>
       <c r="E26">
-        <v>-21.09087163529145</v>
+        <v>-19.97624662846549</v>
       </c>
       <c r="F26">
-        <v>-0.7695766587355268</v>
+        <v>-0.5054384584744597</v>
       </c>
       <c r="G26">
-        <v>-1.867032965723409</v>
+        <v>-2.032076903038235</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.911099045849767</v>
       </c>
       <c r="E27">
-        <v>-20.85543174315866</v>
+        <v>-20.28303262858913</v>
       </c>
       <c r="F27">
-        <v>-0.8010604186137277</v>
+        <v>-0.4386182019276376</v>
       </c>
       <c r="G27">
-        <v>-1.984759275645432</v>
+        <v>-1.88070220825506</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.553300106881013</v>
       </c>
       <c r="E28">
-        <v>-21.60492589074616</v>
+        <v>-20.61181795544202</v>
       </c>
       <c r="F28">
-        <v>-0.8245918514250532</v>
+        <v>-0.3140068935245079</v>
       </c>
       <c r="G28">
-        <v>-3.095986922993816</v>
+        <v>-2.456018743706224</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.429921704819478</v>
       </c>
       <c r="E29">
-        <v>-21.1227249214614</v>
+        <v>-20.16507040916332</v>
       </c>
       <c r="F29">
-        <v>-0.8889377745397132</v>
+        <v>-0.2410558898295667</v>
       </c>
       <c r="G29">
-        <v>-2.467585789820438</v>
+        <v>-2.247931093289794</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.479470644572832</v>
       </c>
       <c r="E30">
-        <v>-21.14607373344495</v>
+        <v>-20.43784304101534</v>
       </c>
       <c r="F30">
-        <v>-0.7568454801219012</v>
+        <v>-0.2780176433424806</v>
       </c>
       <c r="G30">
-        <v>-2.740106588067703</v>
+        <v>-3.213239824903723</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.62981039350118</v>
       </c>
       <c r="E31">
-        <v>-20.67860389010715</v>
+        <v>-20.17978342121424</v>
       </c>
       <c r="F31">
-        <v>-0.7642386591918868</v>
+        <v>-0.454642969334794</v>
       </c>
       <c r="G31">
-        <v>-2.918786662458786</v>
+        <v>-2.291964659507641</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.81967743182787</v>
       </c>
       <c r="E32">
-        <v>-20.21551308113476</v>
+        <v>-20.26752260511286</v>
       </c>
       <c r="F32">
-        <v>-0.9429862624701726</v>
+        <v>-0.4776956057873015</v>
       </c>
       <c r="G32">
-        <v>-3.176684781059091</v>
+        <v>-2.572404282684842</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-12.99532221217196</v>
       </c>
       <c r="E33">
-        <v>-20.01111587832455</v>
+        <v>-19.89448050178299</v>
       </c>
       <c r="F33">
-        <v>-0.97340971207279</v>
+        <v>-0.6355766341890676</v>
       </c>
       <c r="G33">
-        <v>-2.606390343191</v>
+        <v>-3.054558756115377</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-14.11740477099231</v>
       </c>
       <c r="E34">
-        <v>-19.23823669096144</v>
+        <v>-19.85231588029757</v>
       </c>
       <c r="F34">
-        <v>-1.080349458671998</v>
+        <v>-0.7245722861088325</v>
       </c>
       <c r="G34">
-        <v>-2.455912806248968</v>
+        <v>-2.076408418354615</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-15.15074958652258</v>
       </c>
       <c r="E35">
-        <v>-20.14926150640254</v>
+        <v>-18.87550139447304</v>
       </c>
       <c r="F35">
-        <v>-0.9850515875517343</v>
+        <v>-0.8249579898170906</v>
       </c>
       <c r="G35">
-        <v>-2.894192619647541</v>
+        <v>-2.913916849970518</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-16.06889738674668</v>
       </c>
       <c r="E36">
-        <v>-18.11261202077085</v>
+        <v>-18.77704331259827</v>
       </c>
       <c r="F36">
-        <v>-1.313682331957757</v>
+        <v>-0.9731313806254493</v>
       </c>
       <c r="G36">
-        <v>-2.157652516433869</v>
+        <v>-2.801202705994953</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-16.86367069147023</v>
       </c>
       <c r="E37">
-        <v>-19.11532032097125</v>
+        <v>-18.23890210389676</v>
       </c>
       <c r="F37">
-        <v>-1.314427862620277</v>
+        <v>-0.728784534352068</v>
       </c>
       <c r="G37">
-        <v>-3.109599886251299</v>
+        <v>-2.256747076060874</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-17.52905516799452</v>
       </c>
       <c r="E38">
-        <v>-18.75478133437656</v>
+        <v>-17.54998988158388</v>
       </c>
       <c r="F38">
-        <v>-1.693871491881424</v>
+        <v>-1.120596517304415</v>
       </c>
       <c r="G38">
-        <v>-2.237953109034431</v>
+        <v>-2.266566154130352</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-18.06319560801428</v>
       </c>
       <c r="E39">
-        <v>-17.37036796006964</v>
+        <v>-17.44008834589173</v>
       </c>
       <c r="F39">
-        <v>-1.156068866227095</v>
+        <v>-0.9997741614016898</v>
       </c>
       <c r="G39">
-        <v>-2.665013483600414</v>
+        <v>-1.612230207202324</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-18.46452143981416</v>
       </c>
       <c r="E40">
-        <v>-16.65921640190508</v>
+        <v>-17.12113886458349</v>
       </c>
       <c r="F40">
-        <v>-1.118596838394057</v>
+        <v>-1.189543192974223</v>
       </c>
       <c r="G40">
-        <v>-1.567302793688874</v>
+        <v>-1.934879286005233</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-18.73947936784118</v>
       </c>
       <c r="E41">
-        <v>-16.94880778622159</v>
+        <v>-16.43176473792182</v>
       </c>
       <c r="F41">
-        <v>-1.451934366382786</v>
+        <v>-1.089674390525312</v>
       </c>
       <c r="G41">
-        <v>-1.862146600507445</v>
+        <v>-1.369504318808499</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-18.88304409337241</v>
       </c>
       <c r="E42">
-        <v>-17.22510357085159</v>
+        <v>-15.13273574102952</v>
       </c>
       <c r="F42">
-        <v>-1.485302662102356</v>
+        <v>-1.182767147619323</v>
       </c>
       <c r="G42">
-        <v>-1.203381143647871</v>
+        <v>-1.329006415226595</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-18.89315035054056</v>
       </c>
       <c r="E43">
-        <v>-15.25620005637465</v>
+        <v>-16.048705650087</v>
       </c>
       <c r="F43">
-        <v>-1.51488200532152</v>
+        <v>-1.384991511460349</v>
       </c>
       <c r="G43">
-        <v>-1.682115823536338</v>
+        <v>-1.057369532638315</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-18.77059851898172</v>
       </c>
       <c r="E44">
-        <v>-14.93669810123747</v>
+        <v>-14.75414172856626</v>
       </c>
       <c r="F44">
-        <v>-1.680271355862261</v>
+        <v>-1.445421741861976</v>
       </c>
       <c r="G44">
-        <v>-0.7676603819511546</v>
+        <v>-1.738348750066399</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-18.51670657360254</v>
       </c>
       <c r="E45">
-        <v>-14.52531340848467</v>
+        <v>-14.78056990287502</v>
       </c>
       <c r="F45">
-        <v>-1.878593280868699</v>
+        <v>-1.417585283658302</v>
       </c>
       <c r="G45">
-        <v>-1.30304842765317</v>
+        <v>-1.200308957387427</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-18.13589064295848</v>
       </c>
       <c r="E46">
-        <v>-14.97638111896669</v>
+        <v>-14.07172333798037</v>
       </c>
       <c r="F46">
-        <v>-2.021650674597368</v>
+        <v>-1.664111564568449</v>
       </c>
       <c r="G46">
-        <v>-0.905624056754742</v>
+        <v>-0.4480967315908462</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-17.63903462962733</v>
       </c>
       <c r="E47">
-        <v>-14.34335932285647</v>
+        <v>-14.32380537209135</v>
       </c>
       <c r="F47">
-        <v>-1.892060878103414</v>
+        <v>-1.482200426178871</v>
       </c>
       <c r="G47">
-        <v>-1.206105722626691</v>
+        <v>-0.9034986865185299</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-17.04838013099937</v>
       </c>
       <c r="E48">
-        <v>-13.28746409543599</v>
+        <v>-13.09595945812562</v>
       </c>
       <c r="F48">
-        <v>-2.12413546130432</v>
+        <v>-1.67815819061772</v>
       </c>
       <c r="G48">
-        <v>-1.073968607972221</v>
+        <v>-0.9634063185971813</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-16.38017237345764</v>
       </c>
       <c r="E49">
-        <v>-11.93813280926648</v>
+        <v>-13.1234020106121</v>
       </c>
       <c r="F49">
-        <v>-2.118961478506435</v>
+        <v>-1.668924379178714</v>
       </c>
       <c r="G49">
-        <v>-1.814547576743804</v>
+        <v>-0.2450311787574908</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-15.66413741818899</v>
       </c>
       <c r="E50">
-        <v>-11.56840554891023</v>
+        <v>-12.43141948292201</v>
       </c>
       <c r="F50">
-        <v>-2.205380907803493</v>
+        <v>-2.052695399752086</v>
       </c>
       <c r="G50">
-        <v>-0.7463835057702587</v>
+        <v>-0.6999862100373729</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-14.93016155321183</v>
       </c>
       <c r="E51">
-        <v>-11.41873948295673</v>
+        <v>-11.17882998697837</v>
       </c>
       <c r="F51">
-        <v>-1.987283367790023</v>
+        <v>-2.007129394026293</v>
       </c>
       <c r="G51">
-        <v>-1.732091818997176</v>
+        <v>-0.5790718447610321</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-14.2099961077656</v>
       </c>
       <c r="E52">
-        <v>-11.7568353523694</v>
+        <v>-11.80407186474341</v>
       </c>
       <c r="F52">
-        <v>-2.114067483890695</v>
+        <v>-1.840514888096812</v>
       </c>
       <c r="G52">
-        <v>-0.8000375173252268</v>
+        <v>-0.3398948611853067</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-13.52982638483208</v>
       </c>
       <c r="E53">
-        <v>-10.93366293267711</v>
+        <v>-10.83851969377595</v>
       </c>
       <c r="F53">
-        <v>-2.440643048770372</v>
+        <v>-2.1847587013108</v>
       </c>
       <c r="G53">
-        <v>-1.016937839967196</v>
+        <v>-0.3102423047900547</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.92177775602084</v>
       </c>
       <c r="E54">
-        <v>-10.27005582311908</v>
+        <v>-9.89196447127067</v>
       </c>
       <c r="F54">
-        <v>-2.482051478501514</v>
+        <v>-1.718123604333185</v>
       </c>
       <c r="G54">
-        <v>-1.219662406610007</v>
+        <v>-0.4344903894244416</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.41976448146455</v>
       </c>
       <c r="E55">
-        <v>-11.69903391013549</v>
+        <v>-9.202939037107594</v>
       </c>
       <c r="F55">
-        <v>-2.5799007212224</v>
+        <v>-2.205738762521503</v>
       </c>
       <c r="G55">
-        <v>-1.201176320318716</v>
+        <v>-0.9937176735547483</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.04840934782023</v>
       </c>
       <c r="E56">
-        <v>-10.01278868626932</v>
+        <v>-9.205230444955475</v>
       </c>
       <c r="F56">
-        <v>-2.360147274770733</v>
+        <v>-2.333657741964011</v>
       </c>
       <c r="G56">
-        <v>-1.116658092701123</v>
+        <v>-0.8047914607196203</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.83095921045221</v>
       </c>
       <c r="E57">
-        <v>-10.10634695926779</v>
+        <v>-9.073211842209862</v>
       </c>
       <c r="F57">
-        <v>-2.664437271412895</v>
+        <v>-2.529713253756389</v>
       </c>
       <c r="G57">
-        <v>-1.770543805435811</v>
+        <v>-0.2827978822694965</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.7798858223605</v>
       </c>
       <c r="E58">
-        <v>-9.795657414549543</v>
+        <v>-8.80162114207384</v>
       </c>
       <c r="F58">
-        <v>-2.25454037132263</v>
+        <v>-2.684651092776009</v>
       </c>
       <c r="G58">
-        <v>-1.386844956343202</v>
+        <v>-0.7945420117300366</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.90573051320752</v>
       </c>
       <c r="E59">
-        <v>-8.493829820720499</v>
+        <v>-8.529731562653311</v>
       </c>
       <c r="F59">
-        <v>-2.877538927620082</v>
+        <v>-2.329496024132346</v>
       </c>
       <c r="G59">
-        <v>-1.87438568736613</v>
+        <v>-0.2901704671854535</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.19681023807806</v>
       </c>
       <c r="E60">
-        <v>-8.681965273369165</v>
+        <v>-8.099567288190697</v>
       </c>
       <c r="F60">
-        <v>-2.611655357241316</v>
+        <v>-2.422881194919545</v>
       </c>
       <c r="G60">
-        <v>-1.245653499638825</v>
+        <v>-0.6951759873688119</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.64017704395591</v>
       </c>
       <c r="E61">
-        <v>-8.424064150158332</v>
+        <v>-7.858453218126296</v>
       </c>
       <c r="F61">
-        <v>-3.013339822900227</v>
+        <v>-2.31956389897278</v>
       </c>
       <c r="G61">
-        <v>-1.955302041436997</v>
+        <v>-0.8914483007555828</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.2165555816035</v>
       </c>
       <c r="E62">
-        <v>-7.963717596434593</v>
+        <v>-7.290251998961873</v>
       </c>
       <c r="F62">
-        <v>-2.808794373596557</v>
+        <v>-2.436698363198241</v>
       </c>
       <c r="G62">
-        <v>-2.247527206734004</v>
+        <v>-0.8256478976170287</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.90011601395555</v>
       </c>
       <c r="E63">
-        <v>-7.559492421087914</v>
+        <v>-7.026323476846829</v>
       </c>
       <c r="F63">
-        <v>-2.885560837548792</v>
+        <v>-2.622709920231676</v>
       </c>
       <c r="G63">
-        <v>-2.608969258166093</v>
+        <v>-1.047772261119968</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-14.65718888793665</v>
       </c>
       <c r="E64">
-        <v>-6.928494852859126</v>
+        <v>-6.554945560440406</v>
       </c>
       <c r="F64">
-        <v>-2.84269945139314</v>
+        <v>-2.65091914376661</v>
       </c>
       <c r="G64">
-        <v>-1.542947110156456</v>
+        <v>-1.382425378048275</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-15.44946032102469</v>
       </c>
       <c r="E65">
-        <v>-6.583864395453389</v>
+        <v>-6.843499924209161</v>
       </c>
       <c r="F65">
-        <v>-3.020709807682934</v>
+        <v>-2.951319127085226</v>
       </c>
       <c r="G65">
-        <v>-2.74879677010829</v>
+        <v>-1.720183786692418</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-16.24488615911023</v>
       </c>
       <c r="E66">
-        <v>-7.429556916385828</v>
+        <v>-6.033292525600827</v>
       </c>
       <c r="F66">
-        <v>-3.146294447784354</v>
+        <v>-2.551231753778912</v>
       </c>
       <c r="G66">
-        <v>-1.690302802654956</v>
+        <v>-2.026856172722804</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-16.99937165380513</v>
       </c>
       <c r="E67">
-        <v>-6.501052191275121</v>
+        <v>-5.781138035905726</v>
       </c>
       <c r="F67">
-        <v>-3.168617292554995</v>
+        <v>-2.756491255783796</v>
       </c>
       <c r="G67">
-        <v>-2.260663451433832</v>
+        <v>-1.450632547793879</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-17.67436272212726</v>
       </c>
       <c r="E68">
-        <v>-6.829153718552861</v>
+        <v>-5.870081793890379</v>
       </c>
       <c r="F68">
-        <v>-2.864659471241355</v>
+        <v>-2.658033163021852</v>
       </c>
       <c r="G68">
-        <v>-2.229451628089583</v>
+        <v>-1.43377524990791</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-18.23560805979521</v>
       </c>
       <c r="E69">
-        <v>-5.984751812712608</v>
+        <v>-5.536985359782179</v>
       </c>
       <c r="F69">
-        <v>-3.086427507216631</v>
+        <v>-2.800043500353383</v>
       </c>
       <c r="G69">
-        <v>-2.811382633528211</v>
+        <v>-1.60706575616106</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-18.66318782029588</v>
       </c>
       <c r="E70">
-        <v>-6.58740113365338</v>
+        <v>-5.325419582617827</v>
       </c>
       <c r="F70">
-        <v>-2.783127409620814</v>
+        <v>-2.861500077967078</v>
       </c>
       <c r="G70">
-        <v>-2.467923465465443</v>
+        <v>-1.954471094506639</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-18.94143208300775</v>
       </c>
       <c r="E71">
-        <v>-6.97465358841931</v>
+        <v>-6.069565602402267</v>
       </c>
       <c r="F71">
-        <v>-2.936357155055861</v>
+        <v>-3.01447385787466</v>
       </c>
       <c r="G71">
-        <v>-2.690544410799274</v>
+        <v>-1.430501120369571</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-19.06952009233504</v>
       </c>
       <c r="E72">
-        <v>-5.700114578960488</v>
+        <v>-5.147477724960428</v>
       </c>
       <c r="F72">
-        <v>-3.227269846510214</v>
+        <v>-2.948356885252815</v>
       </c>
       <c r="G72">
-        <v>-2.20480130600417</v>
+        <v>-1.50913319801834</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-19.06233961571241</v>
       </c>
       <c r="E73">
-        <v>-6.206461371654141</v>
+        <v>-5.049839296881047</v>
       </c>
       <c r="F73">
-        <v>-3.206050387120102</v>
+        <v>-3.060256895859986</v>
       </c>
       <c r="G73">
-        <v>-1.777436361248574</v>
+        <v>-1.306799275749164</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-18.93840387842326</v>
       </c>
       <c r="E74">
-        <v>-6.17293255010135</v>
+        <v>-5.829334584769362</v>
       </c>
       <c r="F74">
-        <v>-3.598133246213163</v>
+        <v>-3.205282490537706</v>
       </c>
       <c r="G74">
-        <v>-2.185368403688648</v>
+        <v>-0.8202715716612523</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-18.72329409511346</v>
       </c>
       <c r="E75">
-        <v>-6.856560043247282</v>
+        <v>-6.214553754705848</v>
       </c>
       <c r="F75">
-        <v>-3.281038346258527</v>
+        <v>-3.220293336243836</v>
       </c>
       <c r="G75">
-        <v>-0.8149680777073398</v>
+        <v>-0.5427750234684628</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-18.44408445463217</v>
       </c>
       <c r="E76">
-        <v>-6.460948025463193</v>
+        <v>-6.467645638520537</v>
       </c>
       <c r="F76">
-        <v>-3.588430578824173</v>
+        <v>-3.412207011022217</v>
       </c>
       <c r="G76">
-        <v>-1.472190820345613</v>
+        <v>-0.1777013035797934</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-18.13847408223417</v>
       </c>
       <c r="E77">
-        <v>-7.585114527023313</v>
+        <v>-6.952835400650354</v>
       </c>
       <c r="F77">
-        <v>-3.643937821750962</v>
+        <v>-3.330521701432158</v>
       </c>
       <c r="G77">
-        <v>-1.228011602460049</v>
+        <v>0.1658902863045453</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-17.82889042323432</v>
       </c>
       <c r="E78">
-        <v>-7.633551085009355</v>
+        <v>-7.24080559127212</v>
       </c>
       <c r="F78">
-        <v>-3.497589324330971</v>
+        <v>-3.492826211764874</v>
       </c>
       <c r="G78">
-        <v>-1.902263791352333</v>
+        <v>-0.4035036831768632</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-17.54286614263719</v>
       </c>
       <c r="E79">
-        <v>-9.661999504213153</v>
+        <v>-7.543266898718431</v>
       </c>
       <c r="F79">
-        <v>-3.943079514984725</v>
+        <v>-3.55601987582224</v>
       </c>
       <c r="G79">
-        <v>-0.320842671606801</v>
+        <v>0.3510126823150508</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-17.30167974724996</v>
       </c>
       <c r="E80">
-        <v>-8.389131501663162</v>
+        <v>-7.75522665312145</v>
       </c>
       <c r="F80">
-        <v>-3.793271755290643</v>
+        <v>-3.732835726317197</v>
       </c>
       <c r="G80">
-        <v>-0.7272849685542032</v>
+        <v>0.003839082157220663</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-17.11817017120331</v>
       </c>
       <c r="E81">
-        <v>-8.409496049275655</v>
+        <v>-8.772887974495172</v>
       </c>
       <c r="F81">
-        <v>-3.92728006351113</v>
+        <v>-3.505098474837348</v>
       </c>
       <c r="G81">
-        <v>-0.3587186231216026</v>
+        <v>-0.03146788601910654</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-16.99412099957544</v>
       </c>
       <c r="E82">
-        <v>-10.28715081249804</v>
+        <v>-9.647558200602692</v>
       </c>
       <c r="F82">
-        <v>-4.262793712667014</v>
+        <v>-3.9730465341484</v>
       </c>
       <c r="G82">
-        <v>-0.316227771125057</v>
+        <v>0.6594297258446331</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-16.92699175616642</v>
       </c>
       <c r="E83">
-        <v>-11.54544165721734</v>
+        <v>-9.868036014614139</v>
       </c>
       <c r="F83">
-        <v>-3.96693318271574</v>
+        <v>-3.995374349123458</v>
       </c>
       <c r="G83">
-        <v>-0.4640601821812118</v>
+        <v>1.337935965754881</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-16.9166279259946</v>
       </c>
       <c r="E84">
-        <v>-11.82273370612902</v>
+        <v>-11.2296213514484</v>
       </c>
       <c r="F84">
-        <v>-4.328771519565189</v>
+        <v>-4.112685255605715</v>
       </c>
       <c r="G84">
-        <v>-0.3812104695154111</v>
+        <v>1.248004996180579</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-16.94793893293339</v>
       </c>
       <c r="E85">
-        <v>-13.68295384442187</v>
+        <v>-12.72502762368333</v>
       </c>
       <c r="F85">
-        <v>-4.266125406361073</v>
+        <v>-4.407953502863988</v>
       </c>
       <c r="G85">
-        <v>-0.036344319598453</v>
+        <v>1.20425613687911</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-17.01136442039526</v>
       </c>
       <c r="E86">
-        <v>-14.55646025270942</v>
+        <v>-13.60546712567662</v>
       </c>
       <c r="F86">
-        <v>-4.807731066761654</v>
+        <v>-4.764009835241897</v>
       </c>
       <c r="G86">
-        <v>-0.5192337341387054</v>
+        <v>0.8851526523487605</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-17.09501767448861</v>
       </c>
       <c r="E87">
-        <v>-15.35569515879717</v>
+        <v>-15.16394145541638</v>
       </c>
       <c r="F87">
-        <v>-4.601225700182961</v>
+        <v>-4.498733458169383</v>
       </c>
       <c r="G87">
-        <v>-0.5237261444354965</v>
+        <v>1.72490232329475</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-17.19276443927425</v>
       </c>
       <c r="E88">
-        <v>-17.02551560743752</v>
+        <v>-15.99012078184976</v>
       </c>
       <c r="F88">
-        <v>-4.693102413929662</v>
+        <v>-4.85811817077174</v>
       </c>
       <c r="G88">
-        <v>0.02941635699362985</v>
+        <v>1.754011950221562</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-17.29122287661747</v>
       </c>
       <c r="E89">
-        <v>-19.12694491374894</v>
+        <v>-17.59623465815021</v>
       </c>
       <c r="F89">
-        <v>-5.136388318924567</v>
+        <v>-4.995743959440253</v>
       </c>
       <c r="G89">
-        <v>-0.852069361565952</v>
+        <v>0.9152819273016676</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-17.38608600418391</v>
       </c>
       <c r="E90">
-        <v>-19.21828423448365</v>
+        <v>-18.92736147880888</v>
       </c>
       <c r="F90">
-        <v>-4.928401003062264</v>
+        <v>-5.181885570155927</v>
       </c>
       <c r="G90">
-        <v>-0.7943764844530731</v>
+        <v>1.078862603488135</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-17.48080428604693</v>
       </c>
       <c r="E91">
-        <v>-21.88392970283273</v>
+        <v>-21.59706445986884</v>
       </c>
       <c r="F91">
-        <v>-5.255399863684772</v>
+        <v>-5.243411730631458</v>
       </c>
       <c r="G91">
-        <v>-0.419712114137135</v>
+        <v>1.299507153135021</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-17.57829944913597</v>
       </c>
       <c r="E92">
-        <v>-22.75688816576536</v>
+        <v>-23.83869079298372</v>
       </c>
       <c r="F92">
-        <v>-5.270397455512457</v>
+        <v>-5.256234029659391</v>
       </c>
       <c r="G92">
-        <v>-0.5949790160772301</v>
+        <v>0.8165945647759935</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-17.68599320518643</v>
       </c>
       <c r="E93">
-        <v>-25.72724559314257</v>
+        <v>-25.69864375131012</v>
       </c>
       <c r="F93">
-        <v>-5.33013434239794</v>
+        <v>-5.476940098624278</v>
       </c>
       <c r="G93">
-        <v>-1.341685804642003</v>
+        <v>0.6903667739091224</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-17.80974855074744</v>
       </c>
       <c r="E94">
-        <v>-28.28077057353574</v>
+        <v>-26.8801724331254</v>
       </c>
       <c r="F94">
-        <v>-5.657310473644648</v>
+        <v>-5.574221081306843</v>
       </c>
       <c r="G94">
-        <v>-1.350746767782989</v>
+        <v>0.5452986683782589</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-17.96494738690668</v>
       </c>
       <c r="E95">
-        <v>-29.61243628260133</v>
+        <v>-30.24959710395455</v>
       </c>
       <c r="F95">
-        <v>-5.277841164994014</v>
+        <v>-5.631219385558671</v>
       </c>
       <c r="G95">
-        <v>-1.968722993053202</v>
+        <v>0.1100777990579723</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-18.14996590805294</v>
       </c>
       <c r="E96">
-        <v>-31.50536332441458</v>
+        <v>-32.0091537935309</v>
       </c>
       <c r="F96">
-        <v>-5.900066026137251</v>
+        <v>-5.852086986167103</v>
       </c>
       <c r="G96">
-        <v>-1.968123784310594</v>
+        <v>-0.3600329097006933</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-18.36375558247887</v>
       </c>
       <c r="E97">
-        <v>-35.03884328735661</v>
+        <v>-34.37397273355045</v>
       </c>
       <c r="F97">
-        <v>-5.906458537384655</v>
+        <v>-6.367101224570418</v>
       </c>
       <c r="G97">
-        <v>-2.08451925492583</v>
+        <v>-0.5555537292500496</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-18.60552060252373</v>
       </c>
       <c r="E98">
-        <v>-36.99526859170541</v>
+        <v>-36.43679453470947</v>
       </c>
       <c r="F98">
-        <v>-5.696345630766769</v>
+        <v>-6.217317487531017</v>
       </c>
       <c r="G98">
-        <v>-3.470002426384057</v>
+        <v>-1.083357315121594</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-18.85991093111352</v>
       </c>
       <c r="E99">
-        <v>-40.90116572856424</v>
+        <v>-38.90371924241696</v>
       </c>
       <c r="F99">
-        <v>-6.507000881759615</v>
+        <v>-6.408350607760222</v>
       </c>
       <c r="G99">
-        <v>-2.93239631517073</v>
+        <v>-1.837575731514974</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-19.12174512575733</v>
       </c>
       <c r="E100">
-        <v>-41.94642130630371</v>
+        <v>-41.41474902272216</v>
       </c>
       <c r="F100">
-        <v>-6.092567841771619</v>
+        <v>-6.474374803232954</v>
       </c>
       <c r="G100">
-        <v>-3.332392979953172</v>
+        <v>-2.653568927671154</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-19.36127811476516</v>
       </c>
       <c r="E101">
-        <v>-44.81535450133112</v>
+        <v>-45.44875442502098</v>
       </c>
       <c r="F101">
-        <v>-6.060562210429655</v>
+        <v>-6.389545425165569</v>
       </c>
       <c r="G101">
-        <v>-3.200219449297769</v>
+        <v>-2.655260616441721</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-19.60569242485477</v>
       </c>
       <c r="E102">
-        <v>-47.53384273287572</v>
+        <v>-47.45013841931794</v>
       </c>
       <c r="F102">
-        <v>-6.269005128363498</v>
+        <v>-6.78165189272961</v>
       </c>
       <c r="G102">
-        <v>-3.774668621817645</v>
+        <v>-3.140762051412459</v>
       </c>
     </row>
   </sheetData>
